--- a/FORMATO PARA 8.º a 10.º EGB.xlsx
+++ b/FORMATO PARA 8.º a 10.º EGB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33F78D8-0C22-47A8-91A7-EBBDD324C56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028D8AC4-4240-4413-9C2F-89D965DD1D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>UNIDAD EDUCATIVA EMILIANO HINOSTROZA</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN COMPORTAMENTAL</t>
   </si>
 </sst>
 </file>
@@ -235,7 +238,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000000000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,8 +272,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,6 +302,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA9A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9A9A9"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -315,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -335,6 +358,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -683,6 +713,7 @@
     <col min="4" max="4" width="35.88671875" customWidth="1"/>
     <col min="5" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="45" customWidth="1"/>
+    <col min="13" max="13" width="33.109375" customWidth="1"/>
     <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="39.21875" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="33.21875" hidden="1" customWidth="1"/>
@@ -894,6 +925,9 @@
       <c r="L9" s="2" t="s">
         <v>65</v>
       </c>
+      <c r="M9" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="V9" t="s">
         <v>59</v>
       </c>
@@ -917,6 +951,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
+      <c r="M10" s="10"/>
       <c r="W10" t="s">
         <v>41</v>
       </c>
@@ -937,6 +972,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
+      <c r="M11" s="10"/>
       <c r="W11" t="s">
         <v>42</v>
       </c>
@@ -957,6 +993,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
+      <c r="M12" s="10"/>
       <c r="W12" t="s">
         <v>43</v>
       </c>
@@ -977,6 +1014,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
+      <c r="M13" s="10"/>
       <c r="W13" t="s">
         <v>44</v>
       </c>
@@ -997,6 +1035,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
+      <c r="M14" s="10"/>
       <c r="W14" t="s">
         <v>45</v>
       </c>
@@ -1017,6 +1056,7 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
+      <c r="M15" s="10"/>
       <c r="W15" t="s">
         <v>46</v>
       </c>
@@ -1034,6 +1074,7 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
+      <c r="M16" s="10"/>
       <c r="W16" t="s">
         <v>47</v>
       </c>
@@ -1051,6 +1092,7 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
+      <c r="M17" s="11"/>
       <c r="W17" t="s">
         <v>42</v>
       </c>
@@ -1071,6 +1113,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
+      <c r="M18" s="11"/>
       <c r="W18" t="s">
         <v>43</v>
       </c>
@@ -1091,6 +1134,7 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
+      <c r="M19" s="11"/>
       <c r="W19" t="s">
         <v>44</v>
       </c>
@@ -1111,6 +1155,7 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
+      <c r="M20" s="11"/>
       <c r="W20" t="s">
         <v>45</v>
       </c>
@@ -1131,6 +1176,7 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
+      <c r="M21" s="11"/>
       <c r="W21" t="s">
         <v>46</v>
       </c>
@@ -1148,6 +1194,7 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
+      <c r="M22" s="11"/>
       <c r="W22" t="s">
         <v>47</v>
       </c>
@@ -1165,6 +1212,7 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
+      <c r="M23" s="11"/>
       <c r="W23" t="s">
         <v>42</v>
       </c>
@@ -1185,6 +1233,7 @@
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
+      <c r="M24" s="11"/>
       <c r="W24" t="s">
         <v>43</v>
       </c>
@@ -1205,6 +1254,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
+      <c r="M25" s="11"/>
       <c r="W25" t="s">
         <v>44</v>
       </c>
@@ -1225,6 +1275,7 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
+      <c r="M26" s="11"/>
       <c r="W26" t="s">
         <v>45</v>
       </c>
@@ -1245,6 +1296,7 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
+      <c r="M27" s="11"/>
       <c r="W27" t="s">
         <v>46</v>
       </c>
@@ -1262,6 +1314,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
+      <c r="M28" s="11"/>
       <c r="W28" t="s">
         <v>47</v>
       </c>
@@ -1279,6 +1332,7 @@
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
+      <c r="M29" s="11"/>
       <c r="W29" t="s">
         <v>42</v>
       </c>
@@ -1299,6 +1353,7 @@
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
+      <c r="M30" s="11"/>
       <c r="W30" t="s">
         <v>43</v>
       </c>
@@ -1319,6 +1374,7 @@
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
+      <c r="M31" s="11"/>
       <c r="W31" t="s">
         <v>44</v>
       </c>
@@ -1339,6 +1395,7 @@
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
+      <c r="M32" s="11"/>
       <c r="W32" t="s">
         <v>45</v>
       </c>
@@ -1359,6 +1416,7 @@
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
+      <c r="M33" s="11"/>
       <c r="W33" t="s">
         <v>46</v>
       </c>
@@ -1376,6 +1434,7 @@
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
+      <c r="M34" s="11"/>
       <c r="W34" t="s">
         <v>47</v>
       </c>
@@ -1393,6 +1452,7 @@
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
+      <c r="M35" s="11"/>
       <c r="W35" t="s">
         <v>42</v>
       </c>
@@ -1413,6 +1473,7 @@
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
+      <c r="M36" s="11"/>
       <c r="W36" t="s">
         <v>43</v>
       </c>
@@ -1433,6 +1494,7 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
+      <c r="M37" s="11"/>
       <c r="W37" t="s">
         <v>44</v>
       </c>
@@ -1453,6 +1515,7 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
+      <c r="M38" s="11"/>
       <c r="W38" t="s">
         <v>45</v>
       </c>
@@ -1473,6 +1536,7 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
+      <c r="M39" s="11"/>
       <c r="W39" t="s">
         <v>46</v>
       </c>
@@ -1490,6 +1554,7 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
+      <c r="M40" s="11"/>
       <c r="W40" t="s">
         <v>47</v>
       </c>
